--- a/results/marc_powercurve_points.xlsx
+++ b/results/marc_powercurve_points.xlsx
@@ -450,7 +450,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.3887755102040816</v>
+        <v>0.3766326530612245</v>
       </c>
       <c r="B3" t="n">
         <v>11.2219168543719</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.7775510204081633</v>
+        <v>0.7532653061224489</v>
       </c>
       <c r="B4" t="n">
         <v>10.53505745055207</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1.166326530612245</v>
+        <v>1.129897959183673</v>
       </c>
       <c r="B5" t="n">
         <v>9.876812960586152</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1.555102040816327</v>
+        <v>1.506530612244898</v>
       </c>
       <c r="B6" t="n">
         <v>9.246574556519818</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1.943877551020408</v>
+        <v>1.883163265306122</v>
       </c>
       <c r="B7" t="n">
         <v>8.643733410398729</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2.33265306122449</v>
+        <v>2.259795918367347</v>
       </c>
       <c r="B8" t="n">
         <v>8.067680694268544</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2.721428571428572</v>
+        <v>2.636428571428571</v>
       </c>
       <c r="B9" t="n">
         <v>7.51780758017493</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3.110204081632653</v>
+        <v>3.013061224489796</v>
       </c>
       <c r="B10" t="n">
         <v>6.993505240163539</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3.498979591836735</v>
+        <v>3.38969387755102</v>
       </c>
       <c r="B11" t="n">
         <v>6.494164846280038</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3.887755102040816</v>
+        <v>3.766326530612245</v>
       </c>
       <c r="B12" t="n">
         <v>6.019177570570086</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>4.276530612244898</v>
+        <v>4.142959183673469</v>
       </c>
       <c r="B13" t="n">
         <v>5.567934585079346</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>4.66530612244898</v>
+        <v>4.519591836734693</v>
       </c>
       <c r="B14" t="n">
         <v>5.139827061853478</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>5.054081632653062</v>
+        <v>4.896224489795918</v>
       </c>
       <c r="B15" t="n">
         <v>4.734246172938145</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>5.442857142857143</v>
+        <v>5.272857142857142</v>
       </c>
       <c r="B16" t="n">
         <v>4.350583090379009</v>
@@ -562,7 +562,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>5.831632653061225</v>
+        <v>5.649489795918367</v>
       </c>
       <c r="B17" t="n">
         <v>3.988228986221727</v>
@@ -570,7 +570,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>6.220408163265306</v>
+        <v>6.026122448979591</v>
       </c>
       <c r="B18" t="n">
         <v>3.646575032511965</v>
@@ -578,7 +578,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>6.609183673469388</v>
+        <v>6.402755102040816</v>
       </c>
       <c r="B19" t="n">
         <v>3.32501240129538</v>
@@ -586,7 +586,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>6.997959183673469</v>
+        <v>6.77938775510204</v>
       </c>
       <c r="B20" t="n">
         <v>3.022932264617634</v>
@@ -594,7 +594,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>7.386734693877551</v>
+        <v>7.156020408163265</v>
       </c>
       <c r="B21" t="n">
         <v>2.739725794524391</v>
@@ -602,7 +602,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>7.775510204081632</v>
+        <v>7.532653061224489</v>
       </c>
       <c r="B22" t="n">
         <v>2.474784163061309</v>
@@ -610,7 +610,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>8.164285714285715</v>
+        <v>7.909285714285714</v>
       </c>
       <c r="B23" t="n">
         <v>2.227498542274052</v>
@@ -618,7 +618,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>8.553061224489795</v>
+        <v>8.285918367346937</v>
       </c>
       <c r="B24" t="n">
         <v>1.997260104208281</v>
@@ -626,23 +626,23 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>8.941836734693878</v>
+        <v>8.662551020408163</v>
       </c>
       <c r="B25" t="n">
-        <v>1.783460020909655</v>
+        <v>1.783460020909654</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>9.33061224489796</v>
+        <v>9.039183673469386</v>
       </c>
       <c r="B26" t="n">
-        <v>1.585489464423836</v>
+        <v>1.585489464423837</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>9.719387755102041</v>
+        <v>9.415816326530612</v>
       </c>
       <c r="B27" t="n">
         <v>1.402739606796488</v>
@@ -650,7 +650,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>10.10816326530612</v>
+        <v>9.792448979591835</v>
       </c>
       <c r="B28" t="n">
         <v>1.234601620073269</v>
@@ -658,7 +658,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>10.4969387755102</v>
+        <v>10.16908163265306</v>
       </c>
       <c r="B29" t="n">
         <v>1.080466676299841</v>
@@ -666,7 +666,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>10.88571428571429</v>
+        <v>10.54571428571428</v>
       </c>
       <c r="B30" t="n">
         <v>0.9397259475218662</v>
@@ -674,7 +674,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>11.27448979591837</v>
+        <v>10.92234693877551</v>
       </c>
       <c r="B31" t="n">
         <v>0.8117706057850047</v>
@@ -682,7 +682,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>11.66326530612245</v>
+        <v>11.29897959183673</v>
       </c>
       <c r="B32" t="n">
         <v>0.6959918231349183</v>
@@ -690,15 +690,15 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>12.05204081632653</v>
+        <v>11.67561224489796</v>
       </c>
       <c r="B33" t="n">
-        <v>0.5917807716172687</v>
+        <v>0.5917807716172682</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>12.44081632653061</v>
+        <v>12.05224489795918</v>
       </c>
       <c r="B34" t="n">
         <v>0.4985286232777162</v>
@@ -706,7 +706,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>12.82959183673469</v>
+        <v>12.42887755102041</v>
       </c>
       <c r="B35" t="n">
         <v>0.4156265501619225</v>
@@ -714,7 +714,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>13.21836734693878</v>
+        <v>12.80551020408163</v>
       </c>
       <c r="B36" t="n">
         <v>0.3424657243155488</v>
@@ -722,23 +722,23 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>13.60714285714286</v>
+        <v>13.18214285714286</v>
       </c>
       <c r="B37" t="n">
-        <v>0.2784373177842565</v>
+        <v>0.2784373177842568</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>13.99591836734694</v>
+        <v>13.55877551020408</v>
       </c>
       <c r="B38" t="n">
-        <v>0.2229325026137071</v>
+        <v>0.2229325026137068</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>14.38469387755102</v>
+        <v>13.9354081632653</v>
       </c>
       <c r="B39" t="n">
         <v>0.1753424508495611</v>
@@ -746,7 +746,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>14.7734693877551</v>
+        <v>14.31204081632653</v>
       </c>
       <c r="B40" t="n">
         <v>0.1350583345374802</v>
@@ -754,7 +754,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>15.16224489795918</v>
+        <v>14.68867346938775</v>
       </c>
       <c r="B41" t="n">
         <v>0.1014713257231256</v>
@@ -762,15 +762,15 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>15.55102040816326</v>
+        <v>15.06530612244898</v>
       </c>
       <c r="B42" t="n">
-        <v>0.07397259645215866</v>
+        <v>0.07397259645215852</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>15.93979591836735</v>
+        <v>15.4419387755102</v>
       </c>
       <c r="B43" t="n">
         <v>0.05195331877024036</v>
@@ -778,23 +778,23 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>16.32857142857143</v>
+        <v>15.81857142857143</v>
       </c>
       <c r="B44" t="n">
-        <v>0.03480466472303211</v>
+        <v>0.03480466472303202</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>16.71734693877551</v>
+        <v>16.19520408163265</v>
       </c>
       <c r="B45" t="n">
-        <v>0.02191780635619514</v>
+        <v>0.02191780635619508</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>17.10612244897959</v>
+        <v>16.57183673469387</v>
       </c>
       <c r="B46" t="n">
         <v>0.01268391571539074</v>
@@ -802,7 +802,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>17.49489795918367</v>
+        <v>16.9484693877551</v>
       </c>
       <c r="B47" t="n">
         <v>0.006494164846280031</v>
@@ -810,31 +810,31 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>17.88367346938776</v>
+        <v>17.32510204081633</v>
       </c>
       <c r="B48" t="n">
-        <v>0.0027397257945244</v>
+        <v>0.002739725794524385</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>18.27244897959184</v>
+        <v>17.70173469387755</v>
       </c>
       <c r="B49" t="n">
-        <v>0.0008117706057850073</v>
+        <v>0.0008117706057850007</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>18.66122448979592</v>
+        <v>18.07836734693877</v>
       </c>
       <c r="B50" t="n">
-        <v>0.0001014713257231243</v>
+        <v>0.0001014713257231259</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>19.05</v>
+        <v>18.455</v>
       </c>
       <c r="B51" t="n">
         <v>0</v>

--- a/results/marc_powercurve_points.xlsx
+++ b/results/marc_powercurve_points.xlsx
@@ -445,396 +445,396 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>11.938</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.3766326530612245</v>
+        <v>3.789959183673469</v>
       </c>
       <c r="B3" t="n">
-        <v>11.2219168543719</v>
+        <v>9.400164897279193</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.7532653061224489</v>
+        <v>7.579918367346939</v>
       </c>
       <c r="B4" t="n">
-        <v>10.53505745055207</v>
+        <v>8.824809390645052</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1.129897959183673</v>
+        <v>11.36987755102041</v>
       </c>
       <c r="B5" t="n">
-        <v>9.876812960586152</v>
+        <v>8.27342348851244</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1.506530612244898</v>
+        <v>15.15983673469388</v>
       </c>
       <c r="B6" t="n">
-        <v>9.246574556519818</v>
+        <v>7.745497199296212</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1.883163265306122</v>
+        <v>18.94979591836735</v>
       </c>
       <c r="B7" t="n">
-        <v>8.643733410398729</v>
+        <v>7.240520531411232</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2.259795918367347</v>
+        <v>22.73975510204082</v>
       </c>
       <c r="B8" t="n">
-        <v>8.067680694268544</v>
+        <v>6.75798349327236</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2.636428571428571</v>
+        <v>26.52971428571428</v>
       </c>
       <c r="B9" t="n">
-        <v>7.51780758017493</v>
+        <v>6.297376093294462</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3.013061224489796</v>
+        <v>30.31967346938776</v>
       </c>
       <c r="B10" t="n">
-        <v>6.993505240163539</v>
+        <v>5.858188339892393</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3.38969387755102</v>
+        <v>34.10963265306123</v>
       </c>
       <c r="B11" t="n">
-        <v>6.494164846280038</v>
+        <v>5.439910241481016</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3.766326530612245</v>
+        <v>37.89959183673469</v>
       </c>
       <c r="B12" t="n">
-        <v>6.019177570570086</v>
+        <v>5.042031806475194</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>4.142959183673469</v>
+        <v>41.68955102040816</v>
       </c>
       <c r="B13" t="n">
-        <v>5.567934585079346</v>
+        <v>4.664043043289785</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>4.519591836734693</v>
+        <v>45.47951020408163</v>
       </c>
       <c r="B14" t="n">
-        <v>5.139827061853478</v>
+        <v>4.305433960339654</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>4.896224489795918</v>
+        <v>49.2694693877551</v>
       </c>
       <c r="B15" t="n">
-        <v>4.734246172938145</v>
+        <v>3.965694566039659</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>5.272857142857142</v>
+        <v>53.05942857142857</v>
       </c>
       <c r="B16" t="n">
-        <v>4.350583090379009</v>
+        <v>3.644314868804665</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>5.649489795918367</v>
+        <v>56.84938775510204</v>
       </c>
       <c r="B17" t="n">
-        <v>3.988228986221727</v>
+        <v>3.340784877049528</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>6.026122448979591</v>
+        <v>60.63934693877551</v>
       </c>
       <c r="B18" t="n">
-        <v>3.646575032511965</v>
+        <v>3.054594599189113</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>6.402755102040816</v>
+        <v>64.42930612244898</v>
       </c>
       <c r="B19" t="n">
-        <v>3.32501240129538</v>
+        <v>2.785234043638281</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>6.77938775510204</v>
+        <v>68.21926530612245</v>
       </c>
       <c r="B20" t="n">
-        <v>3.022932264617634</v>
+        <v>2.53219321881189</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>7.156020408163265</v>
+        <v>72.00922448979591</v>
       </c>
       <c r="B21" t="n">
-        <v>2.739725794524391</v>
+        <v>2.294962133124804</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>7.532653061224489</v>
+        <v>75.79918367346939</v>
       </c>
       <c r="B22" t="n">
-        <v>2.474784163061309</v>
+        <v>2.073030794991882</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>7.909285714285714</v>
+        <v>79.58914285714286</v>
       </c>
       <c r="B23" t="n">
-        <v>2.227498542274052</v>
+        <v>1.865889212827988</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>8.285918367346937</v>
+        <v>83.37910204081632</v>
       </c>
       <c r="B24" t="n">
-        <v>1.997260104208281</v>
+        <v>1.673027395047981</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>8.662551020408163</v>
+        <v>87.16906122448979</v>
       </c>
       <c r="B25" t="n">
-        <v>1.783460020909654</v>
+        <v>1.493935350066723</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>9.039183673469386</v>
+        <v>90.95902040816327</v>
       </c>
       <c r="B26" t="n">
-        <v>1.585489464423837</v>
+        <v>1.328103086299075</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>9.415816326530612</v>
+        <v>94.74897959183673</v>
       </c>
       <c r="B27" t="n">
-        <v>1.402739606796488</v>
+        <v>1.175020612159899</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>9.792448979591835</v>
+        <v>98.5389387755102</v>
       </c>
       <c r="B28" t="n">
-        <v>1.234601620073269</v>
+        <v>1.034177936064055</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>10.16908163265306</v>
+        <v>102.3288979591837</v>
       </c>
       <c r="B29" t="n">
-        <v>1.080466676299841</v>
+        <v>0.9050650664264036</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>10.54571428571428</v>
+        <v>106.1188571428571</v>
       </c>
       <c r="B30" t="n">
-        <v>0.9397259475218662</v>
+        <v>0.7871720116618077</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>10.92234693877551</v>
+        <v>109.9088163265306</v>
       </c>
       <c r="B31" t="n">
-        <v>0.8117706057850047</v>
+        <v>0.679988780185127</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>11.29897959183673</v>
+        <v>113.6987755102041</v>
       </c>
       <c r="B32" t="n">
-        <v>0.6959918231349183</v>
+        <v>0.5830053804112232</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>11.67561224489796</v>
+        <v>117.4887346938775</v>
       </c>
       <c r="B33" t="n">
-        <v>0.5917807716172682</v>
+        <v>0.4957118207549574</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>12.05224489795918</v>
+        <v>121.278693877551</v>
       </c>
       <c r="B34" t="n">
-        <v>0.4985286232777162</v>
+        <v>0.4175981096311909</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>12.42887755102041</v>
+        <v>125.0686530612245</v>
       </c>
       <c r="B35" t="n">
-        <v>0.4156265501619225</v>
+        <v>0.3481542554547847</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>12.80551020408163</v>
+        <v>128.858612244898</v>
       </c>
       <c r="B36" t="n">
-        <v>0.3424657243155488</v>
+        <v>0.2868702666406004</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>13.18214285714286</v>
+        <v>132.6485714285714</v>
       </c>
       <c r="B37" t="n">
-        <v>0.2784373177842568</v>
+        <v>0.2332361516034988</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>13.55877551020408</v>
+        <v>136.4385306122449</v>
       </c>
       <c r="B38" t="n">
-        <v>0.2229325026137068</v>
+        <v>0.1867419187583404</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>13.9354081632653</v>
+        <v>140.2284897959184</v>
       </c>
       <c r="B39" t="n">
-        <v>0.1753424508495611</v>
+        <v>0.1468775765199875</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>14.31204081632653</v>
+        <v>144.0184489795918</v>
       </c>
       <c r="B40" t="n">
-        <v>0.1350583345374802</v>
+        <v>0.1131331333033005</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>14.68867346938775</v>
+        <v>147.8084081632653</v>
       </c>
       <c r="B41" t="n">
-        <v>0.1014713257231256</v>
+        <v>0.08499859752314087</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>15.06530612244898</v>
+        <v>151.5983673469388</v>
       </c>
       <c r="B42" t="n">
-        <v>0.07397259645215852</v>
+        <v>0.06196397759436967</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>15.4419387755102</v>
+        <v>155.3883265306122</v>
       </c>
       <c r="B43" t="n">
-        <v>0.05195331877024036</v>
+        <v>0.04351928193184817</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>15.81857142857143</v>
+        <v>159.1782857142857</v>
       </c>
       <c r="B44" t="n">
-        <v>0.03480466472303202</v>
+        <v>0.02915451895043728</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>16.19520408163265</v>
+        <v>162.9682448979592</v>
       </c>
       <c r="B45" t="n">
-        <v>0.02191780635619508</v>
+        <v>0.01835969706499844</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>16.57183673469387</v>
+        <v>166.7582040816326</v>
       </c>
       <c r="B46" t="n">
-        <v>0.01268391571539074</v>
+        <v>0.01062482469039261</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>16.9484693877551</v>
+        <v>170.5481632653061</v>
       </c>
       <c r="B47" t="n">
-        <v>0.006494164846280031</v>
+        <v>0.005439910241481011</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>17.32510204081633</v>
+        <v>174.3381224489796</v>
       </c>
       <c r="B48" t="n">
-        <v>0.002739725794524385</v>
+        <v>0.002294962133124799</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>17.70173469387755</v>
+        <v>178.128081632653</v>
       </c>
       <c r="B49" t="n">
-        <v>0.0008117706057850007</v>
+        <v>0.0006799887801851293</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>18.07836734693877</v>
+        <v>181.9180408163265</v>
       </c>
       <c r="B50" t="n">
-        <v>0.0001014713257231259</v>
+        <v>8.499859752313977e-05</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>18.455</v>
+        <v>185.708</v>
       </c>
       <c r="B51" t="n">
         <v>0</v>
